--- a/data/zones.xlsx
+++ b/data/zones.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcel\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54EAC020-7B3F-41A3-B6DA-585A378B01B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{704021CC-8DED-4747-AA35-BA6197D63939}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{EF43FDB2-18D1-4A26-BA6D-D4B76A0E9BFB}"/>
+    <workbookView xWindow="1125" yWindow="1125" windowWidth="28800" windowHeight="15345" xr2:uid="{EF43FDB2-18D1-4A26-BA6D-D4B76A0E9BFB}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="4" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="86">
   <si>
     <t>zone_id</t>
   </si>
@@ -297,9 +297,6 @@
   </si>
   <si>
     <t>Kartenfolie / Masterplan Schumacher Quartier</t>
-  </si>
-  <si>
-    <t>Schumacher Quartier (Ost)</t>
   </si>
 </sst>
 </file>
@@ -1444,37 +1441,17 @@
         <v>85</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="100.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="1">
-        <v>23</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>85</v>
-      </c>
+    <row r="24" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="1"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
